--- a/public/templates/official-oshi-template.xlsx
+++ b/public/templates/official-oshi-template.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
-    <sheet name="작성 가이드" sheetId="2" r:id="rId2"/>
+    <sheet name="official-oshi" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,21 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:K3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,342 +417,109 @@
         <v>이름</v>
       </c>
       <c r="B1" t="str">
+        <v>슬러그</v>
+      </c>
+      <c r="C1" t="str">
         <v>원문명</v>
-      </c>
-      <c r="C1" t="str">
-        <v>슬러그</v>
       </c>
       <c r="D1" t="str">
         <v>별칭</v>
       </c>
       <c r="E1" t="str">
-        <v>생일</v>
+        <v>성별</v>
       </c>
       <c r="F1" t="str">
-        <v>성별</v>
+        <v>포지션</v>
       </c>
       <c r="G1" t="str">
-        <v>나이</v>
+        <v>태그</v>
       </c>
       <c r="H1" t="str">
-        <v>키</v>
+        <v>밈 태그</v>
       </c>
       <c r="I1" t="str">
-        <v>성우</v>
+        <v>소개</v>
       </c>
       <c r="J1" t="str">
-        <v>대표대사</v>
+        <v>상태</v>
       </c>
       <c r="K1" t="str">
-        <v>소개</v>
-      </c>
-      <c r="L1" t="str">
-        <v>상태</v>
-      </c>
-      <c r="M1" t="str">
         <v>우선순위</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>샘플 캐릭터</v>
+        <v>몽키 D. 루피</v>
       </c>
       <c r="B2" t="str">
-        <v>Sample Character</v>
+        <v>monkey-d-luffy</v>
       </c>
       <c r="C2" t="str">
-        <v>sample-character</v>
+        <v>モンキー・D・ルフィ</v>
       </c>
       <c r="D2" t="str">
-        <v>샘플, Sample</v>
+        <v>루피, 밀짚모자</v>
       </c>
       <c r="E2" t="str">
-        <v>04-01</v>
+        <v>남성</v>
       </c>
       <c r="F2" t="str">
-        <v>여성</v>
+        <v>주인공, 리더</v>
       </c>
       <c r="G2" t="str">
-        <v>17세</v>
+        <v>열혈, 순수, 성장형, 먼치킨, 리더</v>
       </c>
       <c r="H2" t="str">
-        <v>160cm</v>
+        <v>세계관 최강자 후보, 밈캐</v>
       </c>
       <c r="I2" t="str">
-        <v>성우명</v>
+        <v>동료와 꿈을 향해 직진하는 최애 등록용 캐릭터 소개</v>
       </c>
       <c r="J2" t="str">
-        <v>Representative quote.</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Short character introduction.</v>
-      </c>
-      <c r="L2" t="str">
+        <v>PUBLISHED</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>캐릭터명</v>
+      </c>
+      <c r="B3" t="str">
+        <v>character-slug</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>별칭1, 별칭2</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>히로인, 조력자</v>
+      </c>
+      <c r="G3" t="str">
+        <v>["다정","갭모에","구원서사"]</v>
+      </c>
+      <c r="H3" t="str">
+        <v>작가가 굴림, 멘탈이 이미 박살남</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>DRAFT</v>
       </c>
-      <c r="M2">
-        <v>0</v>
+      <c r="K3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>컬럼</v>
-      </c>
-      <c r="B1" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C1" t="str">
-        <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>형식</v>
-      </c>
-      <c r="E1" t="str">
-        <v>예시</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>이름</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Primary Korean display name for the character/oshi.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>text</v>
-      </c>
-      <c r="E2" t="str">
-        <v>샘플 캐릭터</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>원문명</v>
-      </c>
-      <c r="B3" t="str">
-        <v>N</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Original name in Japanese, English, or source language.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>text</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Monkey D. Luffy</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>슬러그</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="C4" t="str">
-        <v>URL-safe unique key within the work. Used for upsert matching.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>lowercase letters/numbers/hyphen</v>
-      </c>
-      <c r="E4" t="str">
-        <v>luffy</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>별칭</v>
-      </c>
-      <c r="B5" t="str">
-        <v>N</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Search aliases. Separate multiple values with commas.</v>
-      </c>
-      <c r="D5" t="str">
-        <v>comma-separated text</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Luffy, Mugiwara</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>생일</v>
-      </c>
-      <c r="B6" t="str">
-        <v>N</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Birthday. Use MM-DD when year is not part of canon.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>YYYY-MM-DD or MM-DD</v>
-      </c>
-      <c r="E6" t="str">
-        <v>05-05</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>성별</v>
-      </c>
-      <c r="B7" t="str">
-        <v>N</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Gender display value. Use canon value; leave blank if unclear.</v>
-      </c>
-      <c r="D7" t="str">
-        <v>text</v>
-      </c>
-      <c r="E7" t="str">
-        <v>남성</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>나이</v>
-      </c>
-      <c r="B8" t="str">
-        <v>N</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Age display value. Text is allowed for ambiguous timelines.</v>
-      </c>
-      <c r="D8" t="str">
-        <v>text</v>
-      </c>
-      <c r="E8" t="str">
-        <v>19세</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>키</v>
-      </c>
-      <c r="B9" t="str">
-        <v>N</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Height display value.</v>
-      </c>
-      <c r="D9" t="str">
-        <v>text</v>
-      </c>
-      <c r="E9" t="str">
-        <v>174cm</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>성우</v>
-      </c>
-      <c r="B10" t="str">
-        <v>N</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Voice actor name. Prefer the primary/original voice actor.</v>
-      </c>
-      <c r="D10" t="str">
-        <v>text</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Mayumi Tanaka</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>대표대사</v>
-      </c>
-      <c r="B11" t="str">
-        <v>N</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Representative quote. Keep it short.</v>
-      </c>
-      <c r="D11" t="str">
-        <v>text</v>
-      </c>
-      <c r="E11" t="str">
-        <v>I will become the Pirate King!</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>소개</v>
-      </c>
-      <c r="B12" t="str">
-        <v>N</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Short character intro focused on role, personality, or appeal.</v>
-      </c>
-      <c r="D12" t="str">
-        <v>text</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Captain of the Straw Hat Pirates.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>상태</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Y</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Catalog visibility state. Use DRAFT before publishing.</v>
-      </c>
-      <c r="D13" t="str">
-        <v>DRAFT | PUBLISHED | HIDDEN</v>
-      </c>
-      <c r="E13" t="str">
-        <v>DRAFT</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>우선순위</v>
-      </c>
-      <c r="B14" t="str">
-        <v>N</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Sort priority within this work. Lower numbers appear earlier.</v>
-      </c>
-      <c r="D14" t="str">
-        <v>number</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>